--- a/gisaid_batch_uploader_mira_batch_04.xlsx
+++ b/gisaid_batch_uploader_mira_batch_04.xlsx
@@ -680,7 +680,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Original</t>
@@ -701,7 +700,6 @@
           <t>Quito</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Vultur gryphus</t>
@@ -712,20 +710,11 @@
           <t>Condor</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Flu-0713|A_MP</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Flu-0713</t>
@@ -761,28 +750,11 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr">
         <is>
           <t>Confirmed segments: MP; source institution: Fundacion Condor; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -805,7 +777,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Original</t>
@@ -826,7 +797,6 @@
           <t>Quito</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Vultur gryphus</t>
@@ -837,11 +807,6 @@
           <t>Condor</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Flu-0714|A_MP</t>
@@ -852,9 +817,6 @@
           <t>Flu-0714|A_NS</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Flu-0714</t>
@@ -890,28 +852,11 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
           <t>Confirmed segments: MP,NS; source institution: Fundacion Condor; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -934,7 +879,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Original</t>
@@ -955,7 +899,6 @@
           <t>Quito</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Vultur gryphus</t>
@@ -966,20 +909,11 @@
           <t>Condor</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Flu-0715|A_MP</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Flu-0715</t>
@@ -1015,28 +949,11 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
           <t>Confirmed segments: MP; source institution: Fundacion Condor; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1059,7 +976,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1080,7 +996,6 @@
           <t>Quito</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Vultur gryphus</t>
@@ -1091,20 +1006,11 @@
           <t>Condor</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Flu-0716|A_MP</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Flu-0716</t>
@@ -1140,28 +1046,11 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr">
         <is>
           <t>Confirmed segments: MP; source institution: Fundacion Condor; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1184,7 +1073,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1205,7 +1093,6 @@
           <t>Quito</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Vultur gryphus</t>
@@ -1216,20 +1103,11 @@
           <t>Condor</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Flu-0717|A_MP</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Flu-0717</t>
@@ -1265,28 +1143,11 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr">
         <is>
           <t>Confirmed segments: MP; source institution: Fundacion Condor; originating lab: MAATE; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1309,7 +1170,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1325,8 +1185,6 @@
           <t>Cotopaxi</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -1337,11 +1195,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Flu-0736|A_MP</t>
@@ -1357,8 +1210,6 @@
           <t>Flu-0736|A_NP</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Flu-0736</t>
@@ -1394,28 +1245,11 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1438,7 +1272,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1454,8 +1287,6 @@
           <t>Cotopaxi</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -1466,11 +1297,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Flu-0738|A_MP</t>
@@ -1481,9 +1307,6 @@
           <t>Flu-0738|A_NS</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Flu-0738</t>
@@ -1519,28 +1342,11 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr">
         <is>
           <t>Confirmed segments: MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1563,7 +1369,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1579,8 +1384,6 @@
           <t>Guayas</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -1591,11 +1394,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Flu-0739|A_MP</t>
@@ -1611,8 +1409,6 @@
           <t>Flu-0739|A_NP</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Flu-0739</t>
@@ -1648,28 +1444,11 @@
           <t>2023-08-17</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1692,7 +1471,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1708,8 +1486,6 @@
           <t>Tungurahua</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -1720,20 +1496,11 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Flu-0735|A_NS</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Flu-0735</t>
@@ -1769,28 +1536,11 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
           <t>Confirmed segments: NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1813,7 +1563,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1829,8 +1578,6 @@
           <t>Cotopaxi</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -1841,11 +1588,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Flu-0737|A_MP</t>
@@ -1861,8 +1603,6 @@
           <t>Flu-0737|A_NP</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Flu-0737</t>
@@ -1898,28 +1638,11 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1942,7 +1665,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Original</t>
@@ -1958,8 +1680,6 @@
           <t>Pastaza</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -1970,20 +1690,11 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Flu-0740|A_MP</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Flu-0740</t>
@@ -2019,28 +1730,11 @@
           <t>2024-02-27</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="inlineStr">
         <is>
           <t>Confirmed segments: MP; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2063,7 +1757,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2079,8 +1772,6 @@
           <t>Pastaza</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -2091,11 +1782,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Flu-0741|A_MP</t>
@@ -2106,9 +1792,6 @@
           <t>Flu-0741|A_NS</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Flu-0741</t>
@@ -2144,28 +1827,11 @@
           <t>2024-02-27</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr">
         <is>
           <t>Confirmed segments: MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2188,7 +1854,6 @@
           <t>H5N1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Original</t>
@@ -2204,8 +1869,6 @@
           <t>Pastaza</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Gallus gallus domesticus</t>
@@ -2216,11 +1879,6 @@
           <t>Aves de corral</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Flu-0742|A_MP</t>
@@ -2236,8 +1894,6 @@
           <t>Flu-0742|A_NP</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Flu-0742</t>
@@ -2273,28 +1929,11 @@
           <t>2024-02-27</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr">
         <is>
           <t>Confirmed segments: NP,MP,NS; source institution: Agrocalidad; originating lab: AGROCALIDAD; partial segments only where applicable.</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2489,304 +2128,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Seq_Id</t>
+          <t>&gt;Flu-0713|A_MP</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Flu-0713|A_MP</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>ATGAGCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGAGNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Flu-0714|A_MP</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0714|A_MP</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>NNNNNCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Flu-0714|A_NS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0714|A_NS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>NNNNNCTCCAACACCATGTTAAGCTTTCAGGTAGACTGTTTCCTTTGGCATATTCGCAAGCGATTTGCAGACAATGGACTGGGTGATGCCCCATTCCTCGATCGGCTTCGCCGAGATCAAAAGTCCTTAAAGGGAAGAGGCAACACCCTTGGCCTTGATATCGAAACAGCCACTCTTGTTGGGAAACAGATCGCGGAATGGATCTTAAAAGAGGAATCCAGCGAAACACTTAGAATGACAATTGCATCTGTACCTACCTCGCGCTACCTTTCTGACATGACCCTTGAGGAAATGTCACGAGACTGGTTAATGCTCATGCCTAAGCAAAAGATAATAGGCCCTCTTTGCGTGCGATTGGACCAGGCGATCATGGAAAAGAACACAGTACTGAAAGCGAACTTCAGTGTGCTCTTTAACCGCTTAGAGACCTTGATATTACTAAGGGCTTTCACTGAGGAGGGGACAATAGTTGGAGAAATTTCACCATTACCTTCTCTTCCAGGACATACTTATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATAGTAACACAGTTCGAGTCTCTGAAAATTTACAGAGATTCGCTTGGAGAAACTGTGATGAGAATGGGAGACCTACACTACCTCCAGAGCAGAAATGAAAAGTGGCGAGAGCAATTGGGACAGAAATTTGAGGAAATAAGGTGGTTAATTGAAGAAATGCGGCACAGATTGAAAGCGACAGAGAACAGTTTCGAACAAATAACATTCATGCAAGCCTTACAACTACTGCTTGAAGTAGAACAAGAGATAAGAGCTTTCTCGTTTCAGCNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Flu-0715|A_MP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0715|A_MP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>NNNNNCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Flu-0716|A_MP</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0716|A_MP</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>NNNNNNCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACANNNNNNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Flu-0717|A_MP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0717|A_MP</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>NNNNNNCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGAGNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Flu-0736|A_NP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0736|A_NP</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Flu-0736|A_MP</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0736|A_MP</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Flu-0736|A_NS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0736|A_NS</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Flu-0738|A_MP</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0738|A_MP</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTNN</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Flu-0738|A_NS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0738|A_NS</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Flu-0739|A_NP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0739|A_NP</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Flu-0739|A_MP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0739|A_MP</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Flu-0739|A_NS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0739|A_NS</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Flu-0735|A_NS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0735|A_NS</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Flu-0737|A_NP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0737|A_NP</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Flu-0737|A_MP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0737|A_MP</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Flu-0737|A_NS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0737|A_NS</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Flu-0740|A_MP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0740|A_MP</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Flu-0741|A_MP</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0741|A_MP</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Flu-0741|A_NS</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0741|A_NS</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Flu-0742|A_NP</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0742|A_NP</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGAAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTAAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATAGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGGAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Flu-0742|A_MP</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0742|A_MP</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTATGTTCTCTCTATCGTCCCATCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGGGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAGGAAGTTGCACTCAGTTACTSAACTGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTATGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTATTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Flu-0742|A_NS</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>&gt;Flu-0742|A_NS</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>

--- a/gisaid_batch_uploader_mira_batch_04.xlsx
+++ b/gisaid_batch_uploader_mira_batch_04.xlsx
@@ -2128,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,237 +2137,331 @@
           <t>&gt;Flu-0713|A_MP</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ATGAGCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGAGNNNNNNNNN</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>&gt;Flu-0714|A_MP</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>NNNNNCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>&gt;Flu-0714|A_NS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>NNNNNCTCCAACACCATGTTAAGCTTTCAGGTAGACTGTTTCCTTTGGCATATTCGCAAGCGATTTGCAGACAATGGACTGGGTGATGCCCCATTCCTCGATCGGCTTCGCCGAGATCAAAAGTCCTTAAAGGGAAGAGGCAACACCCTTGGCCTTGATATCGAAACAGCCACTCTTGTTGGGAAACAGATCGCGGAATGGATCTTAAAAGAGGAATCCAGCGAAACACTTAGAATGACAATTGCATCTGTACCTACCTCGCGCTACCTTTCTGACATGACCCTTGAGGAAATGTCACGAGACTGGTTAATGCTCATGCCTAAGCAAAAGATAATAGGCCCTCTTTGCGTGCGATTGGACCAGGCGATCATGGAAAAGAACACAGTACTGAAAGCGAACTTCAGTGTGCTCTTTAACCGCTTAGAGACCTTGATATTACTAAGGGCTTTCACTGAGGAGGGGACAATAGTTGGAGAAATTTCACCATTACCTTCTCTTCCAGGACATACTTATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATAGTAACACAGTTCGAGTCTCTGAAAATTTACAGAGATTCGCTTGGAGAAACTGTGATGAGAATGGGAGACCTACACTACCTCCAGAGCAGAAATGAAAAGTGGCGAGAGCAATTGGGACAGAAATTTGAGGAAATAAGGTGGTTAATTGAAGAAATGCGGCACAGATTGAAAGCGACAGAGAACAGTTTCGAACAAATAACATTCATGCAAGCCTTACAACTACTGCTTGAAGTAGAACAAGAGATAAGAGCTTTCTCGTTTCAGCNNNNNNNN</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>&gt;Flu-0715|A_MP</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>NNNNNCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>&gt;Flu-0716|A_MP</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>NNNNNNCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACANNNNNNNNNNNNNN</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>&gt;Flu-0717|A_MP</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>NNNNNNCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGAGNNNNNNNNN</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>&gt;Flu-0736|A_NP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>&gt;Flu-0736|A_MP</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>&gt;Flu-0736|A_NS</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>&gt;Flu-0738|A_MP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTNN</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>&gt;Flu-0738|A_NS</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>&gt;Flu-0739|A_NP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>&gt;Flu-0739|A_MP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>&gt;Flu-0739|A_NS</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>&gt;Flu-0735|A_NS</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>&gt;Flu-0737|A_NP</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>&gt;Flu-0737|A_MP</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>&gt;Flu-0737|A_NS</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>&gt;Flu-0740|A_MP</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>&gt;Flu-0741|A_MP</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>&gt;Flu-0741|A_NS</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>&gt;Flu-0742|A_NP</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGAAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTAAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATAGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGGAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>&gt;Flu-0742|A_MP</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTATGTTCTCTCTATCGTCCCATCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGGGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAGGAAGTTGCACTCAGTTACTSAACTGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTATGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTATTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>&gt;Flu-0742|A_NS</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>

--- a/gisaid_batch_uploader_mira_batch_04.xlsx
+++ b/gisaid_batch_uploader_mira_batch_04.xlsx
@@ -2128,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,331 +2137,237 @@
           <t>&gt;Flu-0713|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ATGAGCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGAGNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>&gt;Flu-0714|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>NNNNNCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>&gt;Flu-0714|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>NNNNNCTCCAACACCATGTTAAGCTTTCAGGTAGACTGTTTCCTTTGGCATATTCGCAAGCGATTTGCAGACAATGGACTGGGTGATGCCCCATTCCTCGATCGGCTTCGCCGAGATCAAAAGTCCTTAAAGGGAAGAGGCAACACCCTTGGCCTTGATATCGAAACAGCCACTCTTGTTGGGAAACAGATCGCGGAATGGATCTTAAAAGAGGAATCCAGCGAAACACTTAGAATGACAATTGCATCTGTACCTACCTCGCGCTACCTTTCTGACATGACCCTTGAGGAAATGTCACGAGACTGGTTAATGCTCATGCCTAAGCAAAAGATAATAGGCCCTCTTTGCGTGCGATTGGACCAGGCGATCATGGAAAAGAACACAGTACTGAAAGCGAACTTCAGTGTGCTCTTTAACCGCTTAGAGACCTTGATATTACTAAGGGCTTTCACTGAGGAGGGGACAATAGTTGGAGAAATTTCACCATTACCTTCTCTTCCAGGACATACTTATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATAGTAACACAGTTCGAGTCTCTGAAAATTTACAGAGATTCGCTTGGAGAAACTGTGATGAGAATGGGAGACCTACACTACCTCCAGAGCAGAAATGAAAAGTGGCGAGAGCAATTGGGACAGAAATTTGAGGAAATAAGGTGGTTAATTGAAGAAATGCGGCACAGATTGAAAGCGACAGAGAACAGTTTCGAACAAATAACATTCATGCAAGCCTTACAACTACTGCTTGAAGTAGAACAAGAGATAAGAGCTTTCTCGTTTCAGCNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>&gt;Flu-0715|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>NNNNNCCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGANNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>&gt;Flu-0716|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>NNNNNNCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACANNNNNNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>&gt;Flu-0717|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>NNNNNNCTTCTAACCGAGGTCGAAACGTACGTTCTTTCTATCATCCCGTCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTGGAAAGCGTCTTTGCAGGAAAGAACACAGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATCTTGTCACCTCTGACTAAGGGGATTTTAGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCCCTAAATGGGAATGGGGACCCGAACAACATGGATAGAGCAGTTAAACTATACAAGAAGCTTAAAAGAGAAATAACGTTCCATGGGGCCAAGGAGGTGTCACTAAGCTATTCAACTGGTGCACTTGCCAGTTGCATGGGTCTCATATACAACAGGATGGGAACAGTGACTACAGAAGCTGCTTTTGGTCTAGTGTGTGCCACTTGTGAACAGATTGCTGATTCACAGCATCGGTCCCACCGACAGATGGCTACTACCACCAATCCACTAATCAGGCATGAAAATAGAATGGTGCTGGCTAGCACTACGGCAAAGGCTATGGAACAGATGGCTGGATCGAGTGAACAGGCAGCGGAGGCCATGGAGGTTGCTAATCAGACTAGGCAGATGGTACATGCAATGAGAACTATTGGGACTCACCCTAGCTCCAGTGCTGGTCTGAAAGATGACCTTCTTGAAAATTTGCAGGCCTACCAGAAGCGGATGGGAGTGCAGATACAGCGATTCAAGTGATCCTCTCGTCATTGCAGCAAATATCATTGGGATCTTGCACCTGATATTGTGGATTGCTGATCGTCTTTTTTTCAAATGTGTTTATCGTCGCTTTAAATACGGTTTGAAAAGAGGGCCCTCTACGGAAGGAGTGCCTGAGTCCATGAGGGAAGAATATCAACAGGAACAGCAGAATGCTGTGGATGTTGACCATGGTCATTTTGTCAACATAGAGNNNNNNNNN</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>&gt;Flu-0736|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>&gt;Flu-0736|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>&gt;Flu-0736|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>&gt;Flu-0738|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTNN</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>&gt;Flu-0738|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>&gt;Flu-0739|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>&gt;Flu-0739|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>&gt;Flu-0739|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>&gt;Flu-0735|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>&gt;Flu-0737|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGGAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTGAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGATCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATGGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGAAACACTGAAGGCAGAACTTCAGACATGAGAACGGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>&gt;Flu-0737|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>&gt;Flu-0737|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>&gt;Flu-0740|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>&gt;Flu-0741|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTACGTTCTCTCTATCGTCCCGTCGGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGAGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAAGAAGTTGCACTTAGTTACTCAACCGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTGTGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTTTTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCAGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>&gt;Flu-0741|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>&gt;Flu-0742|A_NP</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>ATGGCGTCTCAAGGCACCAAACGATCCTATGAACAAATGGAAACTGGTGGGGAACGCCAGAATGCCACTGAAATCAGAGCATCTGTTGGAAGAATGGTTGGCGGAATAGGAAGATTCTACATACAGATGTGCACTGAGCTCAAACTCAGTGATTATGAAGGGAGGCTGATCCAAAACAGCATAACCATAGAAAGGATGGTTCTCTCGGCATTTGATGAGAGGAGGAACAAGTACCTGGAGGAACATCCCAGTGCCGGAAAGGATCCCAAGAAGACTGGAGGTCCAATCTACAGGAGGAGAGATGGCAAATGGGTAAGAGAGTTGATCCTCTACGACAAAGAAGAGATCAGAAGAATTTGGCGTCAAGCTAATAATGGAGAGGATGCAACTGCTGGTCTCACTCATTTGATGATTTGGCATTCCAATCTGAATGATGCAACATACCAGAGAACAAGGGCACTTGTGCGTACTGGAATGGACCCTAGAATGTGCTCTCTGATGCAAGGCTCAACCCTCCCTAGGAGATCCGGGGCTGCTGGAGCAGCAGTGAAAGGAGTTGGAACAATGGTGATGGAACTAATTCGAATGATCAAGCGAGGGATCAATGATCGGAATTTCTGGAGAGGCGAAAACGGTCGGAGAACCAGGATTGCCTACGAGAGAATGTGCAACATCCTCAAGGGAAAGTTCCAAACAGCAGCACAACGGGCAATGATGGACCAAGTGAGAGAAAGCCGGAATCCTGGGAATGCTGAAATTGAAGATCTCATCTTTCTCGCACGATCTGCTCTCATCCTGAGGGGATCAGTGGCTCATAAGTCCTGTCTGCCTGCTTGCGTATATGGACTTGCTGTAGCCAGTGGATATGACTTTGAAAGAGAGGGATATTCTCTAGTCGGAATTGATCCTTTCCGTCTGCTCCAAAACAGCCAAGTCTTCAGTCTCATCAGACCGAACGAAAATCCAGCTCATAAGAGTCAGCTGGTATGGATGGCATGCCACTCTGCGGCATTTGAGGATCTGAGAGTTTCAAGCTTCATCAGAGGGACAAGAGTAGTCCCAAGAGGACAACTGTCCACCAGAGGAGTTCAGATTGCTTCAAATGAAAACATGGAGACAATAGACTCCAGTACTCTTGAACTGAGGAGCAGATACTGGGCTATAAGAACAAGAAGTGGAGGAAACACTAACCAACAGAGAGCATCTGCAGGACAAATCAGCGTGCAGCCCACATTCTCTGTGCAAAGAAACCTCCCATTCGAGAGAGCAACCATCATGGCAGCATTTACGGGGAACACTGAAGGCAGAACTTCAGACATGAGAACTGAGATCATAAGGATGATGGAAAATGCCAGACCTGAAGATGTGTCTTTCCAGGGGCGGGGAGTCTTCGAGCTCTCGGACGAAAAGGCAACGAACCCGATCGTGCCTTCCTTTGACATGAGTAATGAAGGATCTTATTTCTTCGGAGACAATGCAGAGGAGTATGACAATTAA</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>&gt;Flu-0742|A_MP</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>ATGAGTCTTCTAACCGAGGTCGAAACGTATGTTCTCTCTATCGTCCCATCAGGCCCCCTCAAAGCCGAGATCGCGCAGAGACTTGAAGATGTCTTTGCAGGGAAGAACACCGATCTTGAGGCTCTCATGGAATGGCTAAAGACAAGACCAATACTGTCACCTCTGACTAAGGGGATTTTGGGATTTGTGTTCACGCTCACCGTGCCCAGTGAGCGAGGACTGCAGCGTAGACGCTTTGTCCAAAATGCTCTAAGTGGAAATGGGGACCCAAACAACATGGACAGGGCAGTCAAGTTGTACAGGAAACTGAAGAGAGAAATAACATTCCATGGGGCTAAGGAAGTTGCACTCAGTTACTSAACTGGTGCACTTGCCAGTTGTATGGGTCTCATATACAACAGGATGGGGACGGTGACCGCAGAAGTGGCATTGGGCCTAGTATGTGCCACCTGTGAGCAGATTGCTGATTCACAGCATCGGTCTCACAGACAGATAGCTACCACCACCAACCCACTAATCAGACATGAAAACAGAATGGTATTGGCCAGTACTACAGCTAAGGCTATGGAGCAGATGGCTGGATCGAGTGAGCAAGCAGTGGAAGCCATGGAGGTTGCTAGTCAGGCTAGGCAAATGGTGCAGGCGATGAGGACCATTGGAACTCATCCTAGCTCCAGTGCCGGTCTGAGAGATGATCTCCTTGAAAATTTGCAGGCCTACCAAAAACGAATGGGAGTGCAACTGCAGCGATTCAAGTGATCCTCTCGTTATTGCCGCAAGTATCATTGGGATCTTGCACTTGATATTGTGGATTCTTGATCGCCTTTTCTTCAAATGCGTTTATCGTCGCCTTAAATACGGTTTGAAAGGAGGGCCTTCTACGGAAGGAGTACCTGAGTCCATGAGGGAAGAGTACCGGCAGGAACAGCAGAGTGCTGTGGATGTTGACGATGGTCATTTTGTCAACATAGAGATGGAGTAA</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>&gt;Flu-0742|A_NS</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>ATGGATTCCAACACTGTGTCAAGCTTTCAGGTAGACTGCTTTCTTTGGCATGTCCGCAAACAATTTGCAGACCAAGAACTGGGTGATGCCCCATTCCTTGACCGGCTCCGCCGAGACCAGAAGTCTCTAAGAGGAAGAGGCAGCACTCTTGGTCTGGACATCGAGACGGCCACTCGTGCTGGAAAGCAGATAGTGGAGAGGATTCTGGAGGAAGAATCCGACGAGGCACTCAAAATGACTATTGCCTCTGTGCCTGCTCCACGCTACCTAACTGACATGACTCTTGAAGAGATGTCAAGAGACTGGTTCATGCTCATGCCCAAGCAAAAAGTGGCAGGCTCCCTCTGTATCAGAATGGACCAGGCGATTATGGATAAGAACATCATACTGAAGGCAAACTTCAGTGTGATCTTCAATCGGCTGGAGACACTAATACTACTCAGAGCTTTCACTGAAGAGGGAGCAATTGTCGGCGAAATTTCACCATTGCCTTCTCTTCCAGGACATACTGATGAGGATGTCAAAAATGCAATTGGGGTCCTCATCGGAGGACTTGAATGGAATGATAACACAGTTCGAGTCTCTGAAATTTTACAGAGATTCGCTTGGAGAAGCAGTAATGAGGATGGGAGACCTCCACTCCCTCCAAAGCAGAAACGGAAAATGGAGAGAACAATTGAGTCAGAAGTTTGAAGAAATAAGGTGGCTGATTGAAGAGGTGCGACACAGACTAAAGATCACAGAAAATAGTTTTGAACAAATAACATTTATGCAAGCCTTACAACTACTGCTTGAAGTGGAGCAAGAGATACGAACTTTCTCGTTTCAGCTTATTTAA</t>
         </is>
